--- a/output/Data and Chart Outputs/north_america_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/north_america_power_by_type.xlsx
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mmm/yy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,11 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -384,7 +384,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -422,6 +422,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -681,7 +687,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -719,6 +725,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1113,6 +1125,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1127,6 +1140,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1201,7 +1215,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1227,7 +1241,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1253,7 +1267,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1279,7 +1293,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1305,7 +1319,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1331,7 +1345,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1357,7 +1371,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1383,7 +1397,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1409,7 +1423,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1435,7 +1449,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1461,7 +1475,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1487,7 +1501,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1513,7 +1527,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1539,7 +1553,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1565,7 +1579,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1591,7 +1605,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1617,7 +1631,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1643,7 +1657,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1669,7 +1683,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1695,7 +1709,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1721,7 +1735,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1747,7 +1761,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1773,7 +1787,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1799,7 +1813,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1825,7 +1839,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1851,7 +1865,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1877,7 +1891,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1903,7 +1917,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1929,7 +1943,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1955,7 +1969,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1981,7 +1995,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2007,7 +2021,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2033,7 +2047,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2059,7 +2073,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2085,7 +2099,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2111,7 +2125,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2137,7 +2151,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2163,7 +2177,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2189,7 +2203,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2215,7 +2229,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2241,7 +2255,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2267,7 +2281,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2293,7 +2307,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2319,7 +2333,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2345,7 +2359,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2371,7 +2385,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2397,7 +2411,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2423,7 +2437,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2449,7 +2463,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2475,7 +2489,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2501,7 +2515,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2527,7 +2541,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2553,7 +2567,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2579,7 +2593,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2605,7 +2619,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2631,7 +2645,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2657,7 +2671,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2683,7 +2697,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2709,7 +2723,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2735,7 +2749,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2761,7 +2775,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2787,7 +2801,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2813,7 +2827,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2839,7 +2853,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2925,7 +2939,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -2951,7 +2965,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -2977,7 +2991,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -3003,7 +3017,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -3029,7 +3043,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -3055,7 +3069,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -3081,7 +3095,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -3107,7 +3121,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -3133,7 +3147,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -3159,7 +3173,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -3185,7 +3199,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -3211,7 +3225,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -3237,7 +3251,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -3263,7 +3277,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -3289,7 +3303,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -3315,7 +3329,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -3341,7 +3355,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -3367,7 +3381,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -3393,7 +3407,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -3419,7 +3433,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -3445,7 +3459,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -3471,7 +3485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -3497,7 +3511,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -3523,7 +3537,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -3549,7 +3563,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -3575,7 +3589,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -3601,7 +3615,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -3627,7 +3641,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -3653,7 +3667,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -3679,7 +3693,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -3705,7 +3719,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -3731,7 +3745,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -3757,7 +3771,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -3783,7 +3797,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -3809,7 +3823,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -3835,7 +3849,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -3861,7 +3875,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -3887,7 +3901,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -3913,7 +3927,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -3939,7 +3953,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -3965,7 +3979,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -3991,7 +4005,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -4017,7 +4031,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -4043,7 +4057,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -4069,7 +4083,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -4095,7 +4109,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -4121,7 +4135,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -4147,7 +4161,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -4173,7 +4187,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -4199,7 +4213,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -4225,7 +4239,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -4251,7 +4265,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -4277,7 +4291,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -4303,7 +4317,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -4329,7 +4343,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -4355,7 +4369,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -4381,7 +4395,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -4407,7 +4421,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -4433,7 +4447,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -4459,7 +4473,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -4485,7 +4499,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -4511,7 +4525,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -4537,7 +4551,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -4563,7 +4577,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -4589,7 +4603,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">

--- a/output/Data and Chart Outputs/north_america_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/north_america_power_by_type.xlsx
@@ -154,6 +154,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Canada power generation by type (to Apr/26)</a:t>
             </a:r>
           </a:p>
@@ -457,6 +458,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Mexico power generation by type (to May/26)</a:t>
             </a:r>
           </a:p>
@@ -1136,7 +1138,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly. Canada: 2021-01 to 2026-04; Mexico: 2021-01 to 2026-05. Ember lags real time by one to several months (it varies by country); the weekly run picks up new months as they're released.</t>
+          <t>Monthly. Canada: 2021-01 to 2026-04; Mexico: 2021-01 to 2026-05. Ember lags real time by one to several months (it varies by country); each scheduled run picks up new months as they're released.</t>
         </is>
       </c>
     </row>
